--- a/UserLogin.xlsx
+++ b/UserLogin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PythonWork\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD94EE8C-E1FA-4DF5-A6D5-9FB190C929CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8231FC7C-DFF9-4E6C-9723-E7C47E062BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{3A4AC30D-BF5B-4C47-ADF1-7F5ED2D7A8E5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>User</t>
   </si>
@@ -57,13 +57,19 @@
   </si>
   <si>
     <t>Member</t>
+  </si>
+  <si>
+    <t>admin@ztesolar</t>
+  </si>
+  <si>
+    <t>ztesolarbts</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="9"/>
       <color theme="1"/>
@@ -74,6 +80,13 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color theme="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -101,15 +114,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -465,8 +481,8 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
+      <c r="B2" s="3" t="s">
+        <v>7</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -477,13 +493,16 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{6E2DC83B-B809-43B0-B935-B6CC76BD95AE}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/UserLogin.xlsx
+++ b/UserLogin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PythonWork\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8231FC7C-DFF9-4E6C-9723-E7C47E062BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7079AF86-F152-4ACE-A331-EE71C013D046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{3A4AC30D-BF5B-4C47-ADF1-7F5ED2D7A8E5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
   <si>
     <t>User</t>
   </si>
@@ -62,14 +62,56 @@
     <t>admin@ztesolar</t>
   </si>
   <si>
-    <t>ztesolarbts</t>
+    <t>user2</t>
+  </si>
+  <si>
+    <t>ztesolarbts2</t>
+  </si>
+  <si>
+    <t>ztesolarbts1</t>
+  </si>
+  <si>
+    <t>user3</t>
+  </si>
+  <si>
+    <t>user4</t>
+  </si>
+  <si>
+    <t>user5</t>
+  </si>
+  <si>
+    <t>user6</t>
+  </si>
+  <si>
+    <t>user7</t>
+  </si>
+  <si>
+    <t>user8</t>
+  </si>
+  <si>
+    <t>ztesolarbts3</t>
+  </si>
+  <si>
+    <t>ztesolarbts4</t>
+  </si>
+  <si>
+    <t>ztesolarbts5</t>
+  </si>
+  <si>
+    <t>ztesolarbts6</t>
+  </si>
+  <si>
+    <t>ztesolarbts7</t>
+  </si>
+  <si>
+    <t>ztesolarbts8</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="9"/>
       <color theme="1"/>
@@ -87,6 +129,11 @@
       <u/>
       <sz val="9"/>
       <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -458,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{858E05FA-971E-4AAD-A24C-B93FA9129259}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="11.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.8984375" customWidth="1"/>
@@ -493,13 +540,91 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{6E2DC83B-B809-43B0-B935-B6CC76BD95AE}"/>
   </hyperlinks>

--- a/UserLogin.xlsx
+++ b/UserLogin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PythonWork\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7079AF86-F152-4ACE-A331-EE71C013D046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6FDDCD8-0707-4FEE-9181-85C76C132DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{3A4AC30D-BF5B-4C47-ADF1-7F5ED2D7A8E5}"/>
   </bookViews>
@@ -53,9 +53,6 @@
     <t>Admin</t>
   </si>
   <si>
-    <t>user1</t>
-  </si>
-  <si>
     <t>Member</t>
   </si>
   <si>
@@ -105,6 +102,9 @@
   </si>
   <si>
     <t>ztesolarbts8</t>
+  </si>
+  <si>
+    <t>Dechaphop</t>
   </si>
 </sst>
 </file>
@@ -529,7 +529,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -537,90 +537,90 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/UserLogin.xlsx
+++ b/UserLogin.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PythonWork\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SolarBTS Web\PythonWork\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6FDDCD8-0707-4FEE-9181-85C76C132DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24215950-ADEE-4847-892C-5C580C7966FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{3A4AC30D-BF5B-4C47-ADF1-7F5ED2D7A8E5}"/>
   </bookViews>
@@ -59,9 +59,6 @@
     <t>admin@ztesolar</t>
   </si>
   <si>
-    <t>user2</t>
-  </si>
-  <si>
     <t>ztesolarbts2</t>
   </si>
   <si>
@@ -105,6 +102,9 @@
   </si>
   <si>
     <t>Dechaphop</t>
+  </si>
+  <si>
+    <t>Piyaphum</t>
   </si>
 </sst>
 </file>
@@ -537,10 +537,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -548,21 +548,21 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -570,10 +570,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -581,10 +581,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
@@ -592,10 +592,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -603,10 +603,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -614,10 +614,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
